--- a/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20220826120000</t>
+    <t>20250915120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T12:00:00+01:00</t>
+    <t>2025-09-15T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Provisoire</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>Prévisionnelle</t>
   </si>
   <si>
     <t/>
@@ -403,7 +409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -471,15 +477,23 @@
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250915120000</t>
+    <t>20250923120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-15T12:00:00+01:00</t>
+    <t>2025-09-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type de fermeture, codes provenant du FINESS pour les EJ et EG</t>
+    <t>Type de fermeture, codes provenant du FINESS pour les EJ et EG, les différentes valeurs que peuvent nous envoyer FINESS (il en existe davantage)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J201-TypeFermeture-ROR.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type de fermeture, codes provenant du FINESS pour les EJ et EG, les différentes valeurs que peuvent nous envoyer FINESS (il en existe davantage)</t>
+    <t>Différentes valeurs de type de fermeture que peuvent envoyer FINESS au ROR (il en existe davantage)</t>
   </si>
   <si>
     <t>Purpose</t>
